--- a/data/trans_orig/P6714-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P6714-Provincia-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se sienten comprometidos con su profesión en 2012</t>
+          <t>Población según si se sienten comprometidos con su profesión en 2012 (tasa de respuesta: 99,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1658</t>
+          <t>1847</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10716</t>
+          <t>10066</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>1127</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8325</t>
+          <t>10140</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3892</t>
+          <t>3764</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15745</t>
+          <t>15279</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2425</t>
+          <t>2457</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14462</t>
+          <t>14493</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1140</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9831</t>
+          <t>9657</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4841</t>
+          <t>4820</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19728</t>
+          <t>19655</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11431</t>
+          <t>10893</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29102</t>
+          <t>28660</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>3335</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15033</t>
+          <t>14366</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17657</t>
+          <t>17602</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>38614</t>
+          <t>39466</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,41%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5850</t>
+          <t>5241</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18935</t>
+          <t>18495</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4965</t>
+          <t>4219</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15852</t>
+          <t>15926</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12762</t>
+          <t>12638</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30102</t>
+          <t>30096</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>73443</t>
+          <t>74574</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>95917</t>
+          <t>96380</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53993</t>
+          <t>53750</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>70941</t>
+          <t>71021</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>61,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>132793</t>
+          <t>133749</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>161325</t>
+          <t>162864</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>62,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>75,97%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1821</t>
+          <t>1084</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10190</t>
+          <t>9540</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>941</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8475</t>
+          <t>8219</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3746</t>
+          <t>3232</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14436</t>
+          <t>14635</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9862</t>
+          <t>9369</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10242</t>
+          <t>8875</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2091</t>
+          <t>2876</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14185</t>
+          <t>14577</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6668</t>
+          <t>6871</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21282</t>
+          <t>21620</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3432</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16306</t>
+          <t>15934</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12898</t>
+          <t>12846</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>32068</t>
+          <t>31363</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,63%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10861</t>
+          <t>10385</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28015</t>
+          <t>27440</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13281</t>
+          <t>13152</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31077</t>
+          <t>31145</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28119</t>
+          <t>27716</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53502</t>
+          <t>50524</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,13%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>121842</t>
+          <t>120468</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>143667</t>
+          <t>143030</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>76660</t>
+          <t>76508</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>98017</t>
+          <t>97280</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>202647</t>
+          <t>204596</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>235589</t>
+          <t>234735</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,59%</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11704</t>
+          <t>10362</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4075</t>
+          <t>4595</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>922</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11588</t>
+          <t>11641</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>938</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8551</t>
+          <t>9274</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>945</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7869</t>
+          <t>7794</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2838</t>
+          <t>2854</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12495</t>
+          <t>13221</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,89%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10163</t>
+          <t>10308</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25723</t>
+          <t>25403</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13048</t>
+          <t>12126</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27419</t>
+          <t>27956</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>26132</t>
+          <t>26341</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>47518</t>
+          <t>48371</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,55%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>28790</t>
+          <t>29395</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50882</t>
+          <t>50415</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11687</t>
+          <t>11938</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27366</t>
+          <t>27373</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>45861</t>
+          <t>47589</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>73306</t>
+          <t>72558</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,32%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>68687</t>
+          <t>67814</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>92018</t>
+          <t>90957</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,26%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>31028</t>
+          <t>30614</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>48650</t>
+          <t>48114</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>37,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>103203</t>
+          <t>102949</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>133821</t>
+          <t>133175</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>45,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>59,32%</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5277</t>
+          <t>5270</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,62 +2812,62 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>4573</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>2,02%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>1015</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>4546</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1063</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12118</t>
+          <t>13322</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1104</t>
+          <t>925</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>10278</t>
+          <t>9937</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3882</t>
+          <t>3616</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>16642</t>
+          <t>17095</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>10972</t>
+          <t>11300</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28344</t>
+          <t>28455</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14170</t>
+          <t>13972</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>32058</t>
+          <t>31344</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>29621</t>
+          <t>28203</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>52816</t>
+          <t>54146</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>22,26%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>26513</t>
+          <t>26856</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>47465</t>
+          <t>48807</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13505</t>
+          <t>13663</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>30104</t>
+          <t>29892</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>45023</t>
+          <t>45006</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>71187</t>
+          <t>73183</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>30,09%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>71414</t>
+          <t>69832</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>94931</t>
+          <t>95020</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>43874</t>
+          <t>43600</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>64901</t>
+          <t>64138</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>120336</t>
+          <t>120159</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>151378</t>
+          <t>153292</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>63,02%</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7983</t>
+          <t>7148</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5820</t>
+          <t>6166</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9892</t>
+          <t>9152</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2074</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1767</t>
+          <t>1784</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12336</t>
+          <t>12102</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1787</t>
+          <t>1192</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>12509</t>
+          <t>12450</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,03%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6506</t>
+          <t>6904</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>21265</t>
+          <t>21113</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8977</t>
+          <t>8515</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>22041</t>
+          <t>21271</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>18677</t>
+          <t>18309</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>38598</t>
+          <t>37959</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,52%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>9464</t>
+          <t>9387</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>24089</t>
+          <t>23130</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>5881</t>
+          <t>5965</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>17843</t>
+          <t>17610</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>17352</t>
+          <t>17846</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>36861</t>
+          <t>35801</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>25,95%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>42425</t>
+          <t>42603</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>61014</t>
+          <t>60955</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>74,05%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>16277</t>
+          <t>15927</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>30684</t>
+          <t>30520</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>54,86%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>62481</t>
+          <t>64140</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>87222</t>
+          <t>87879</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>63,7%</t>
         </is>
       </c>
     </row>
@@ -4141,97 +4141,97 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>2061</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>1996</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>3,61%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>2055</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>7107</t>
+          <t>5988</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>7957</t>
+          <t>7374</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1106</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>10496</t>
+          <t>10349</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>10549</t>
+          <t>9830</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>25451</t>
+          <t>25227</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>5791</t>
+          <t>5971</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>17810</t>
+          <t>18041</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>18736</t>
+          <t>19253</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>38041</t>
+          <t>37666</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,7%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>12197</t>
+          <t>12346</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>30602</t>
+          <t>30157</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>6112</t>
+          <t>5893</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>17732</t>
+          <t>17752</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>21346</t>
+          <t>21880</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>42744</t>
+          <t>43732</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>25,2%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>68411</t>
+          <t>68701</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>89095</t>
+          <t>90014</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>23087</t>
+          <t>23460</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>38338</t>
+          <t>38585</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>97409</t>
+          <t>97050</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>123204</t>
+          <t>122774</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>70,74%</t>
         </is>
       </c>
     </row>
@@ -4828,7 +4828,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>6050</t>
+          <t>6886</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4843,7 +4843,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1874</t>
+          <t>1892</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>11602</t>
+          <t>10807</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>3022</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>14007</t>
+          <t>13799</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -4936,12 +4936,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>7465</t>
+          <t>7039</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>23947</t>
+          <t>22816</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4951,12 +4951,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>5348</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>20338</t>
+          <t>19514</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>15389</t>
+          <t>16654</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>37379</t>
+          <t>36806</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -5049,12 +5049,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>39544</t>
+          <t>39898</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>65223</t>
+          <t>66897</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>26487</t>
+          <t>27031</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>49476</t>
+          <t>50119</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>72640</t>
+          <t>70843</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>108781</t>
+          <t>107316</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,74%</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5162,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>40785</t>
+          <t>40070</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>67017</t>
+          <t>67323</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5177,12 +5177,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>31767</t>
+          <t>30314</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>55004</t>
+          <t>53625</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>79589</t>
+          <t>76513</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>114947</t>
+          <t>111438</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>24,65%</t>
         </is>
       </c>
     </row>
@@ -5275,12 +5275,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>132766</t>
+          <t>132763</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>166804</t>
+          <t>165008</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5295,7 +5295,7 @@
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>73347</t>
+          <t>74087</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>101962</t>
+          <t>101938</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5325,12 +5325,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>55,97%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>213410</t>
+          <t>214471</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>258773</t>
+          <t>259975</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5360,12 +5360,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>57,5%</t>
         </is>
       </c>
     </row>
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>1950</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>12348</t>
+          <t>11092</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>9399</t>
+          <t>9589</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>4072</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>15989</t>
+          <t>16595</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>8398</t>
+          <t>8656</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>25440</t>
+          <t>26236</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>3018</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>17278</t>
+          <t>16138</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>13523</t>
+          <t>14895</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>35080</t>
+          <t>35739</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>35610</t>
+          <t>34525</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>62970</t>
+          <t>62809</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>25281</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>48251</t>
+          <t>47724</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>64559</t>
+          <t>65832</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>101305</t>
+          <t>99910</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,07%</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>109582</t>
+          <t>109583</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>146459</t>
+          <t>147962</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>89876</t>
+          <t>89854</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>122890</t>
+          <t>122656</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>212045</t>
+          <t>211413</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>265158</t>
+          <t>260520</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>41,9%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>146425</t>
+          <t>145190</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>185563</t>
+          <t>186826</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>51,58%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>90024</t>
+          <t>90307</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>124093</t>
+          <t>123668</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>245874</t>
+          <t>247233</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>297193</t>
+          <t>298187</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>47,95%</t>
         </is>
       </c>
     </row>
@@ -6187,12 +6187,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>13967</t>
+          <t>14481</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>33577</t>
+          <t>33441</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6202,12 +6202,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6222,12 +6222,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>10896</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>27404</t>
+          <t>28388</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6257,12 +6257,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>29857</t>
+          <t>28500</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>56367</t>
+          <t>55319</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -6300,12 +6300,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>37093</t>
+          <t>37814</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>67962</t>
+          <t>66223</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6315,12 +6315,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6335,12 +6335,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>28260</t>
+          <t>28133</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>54799</t>
+          <t>55537</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>70117</t>
+          <t>72187</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>111170</t>
+          <t>113893</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -6413,12 +6413,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>170009</t>
+          <t>168176</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>223968</t>
+          <t>221423</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6428,12 +6428,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>133460</t>
+          <t>133635</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>181280</t>
+          <t>177963</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6483,12 +6483,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>315519</t>
+          <t>314423</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>387436</t>
+          <t>388836</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,46%</t>
         </is>
       </c>
     </row>
@@ -6526,12 +6526,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>289762</t>
+          <t>291319</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>356002</t>
+          <t>359715</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6561,12 +6561,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>211470</t>
+          <t>213748</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>268045</t>
+          <t>267521</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6596,12 +6596,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>523105</t>
+          <t>520028</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>608341</t>
+          <t>605764</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,64%</t>
         </is>
       </c>
     </row>
@@ -6639,12 +6639,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>786794</t>
+          <t>788887</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>865281</t>
+          <t>865000</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6674,12 +6674,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>457325</t>
+          <t>460768</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>523812</t>
+          <t>524402</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6709,12 +6709,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1265877</t>
+          <t>1268668</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>1372103</t>
+          <t>1371607</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>58,06%</t>
         </is>
       </c>
     </row>
@@ -6910,7 +6910,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se sienten comprometidos con su profesión en 2016</t>
+          <t>Población según si se sienten comprometidos con su profesión en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7105,12 +7105,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2632</t>
+          <t>2722</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14278</t>
+          <t>14394</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>949</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11212</t>
+          <t>10328</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4861</t>
+          <t>5033</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19783</t>
+          <t>19841</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -7218,12 +7218,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7653</t>
+          <t>8256</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23618</t>
+          <t>24004</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7233,12 +7233,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2248</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12844</t>
+          <t>12478</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13272</t>
+          <t>12913</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32453</t>
+          <t>32084</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7303,12 +7303,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -7331,12 +7331,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15362</t>
+          <t>16536</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35531</t>
+          <t>36103</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7346,12 +7346,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9531</t>
+          <t>9657</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23436</t>
+          <t>24162</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7381,12 +7381,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>29970</t>
+          <t>29687</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>53182</t>
+          <t>54351</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,92%</t>
         </is>
       </c>
     </row>
@@ -7444,12 +7444,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17909</t>
+          <t>17217</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38745</t>
+          <t>36807</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12222</t>
+          <t>12469</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28172</t>
+          <t>29123</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7494,12 +7494,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35185</t>
+          <t>33521</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61083</t>
+          <t>60110</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7529,12 +7529,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,35%</t>
         </is>
       </c>
     </row>
@@ -7557,12 +7557,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>49610</t>
+          <t>50476</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>75723</t>
+          <t>74680</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>45974</t>
+          <t>46252</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>65722</t>
+          <t>65965</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7607,12 +7607,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,53%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>65,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>101067</t>
+          <t>102958</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>133452</t>
+          <t>134147</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7642,12 +7642,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>56,57%</t>
         </is>
       </c>
     </row>
@@ -7792,7 +7792,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7821</t>
+          <t>7454</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>989</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8296</t>
+          <t>8324</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7837,12 +7837,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11620</t>
+          <t>11806</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7872,12 +7872,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -7900,12 +7900,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2051</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11402</t>
+          <t>11353</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2231</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12794</t>
+          <t>13203</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6156</t>
+          <t>6331</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>19514</t>
+          <t>20421</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -8013,12 +8013,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26405</t>
+          <t>27851</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48950</t>
+          <t>49668</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8028,12 +8028,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>5081</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18473</t>
+          <t>17540</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>36252</t>
+          <t>36166</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>60407</t>
+          <t>63513</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>22,37%</t>
         </is>
       </c>
     </row>
@@ -8126,12 +8126,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26618</t>
+          <t>25995</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47969</t>
+          <t>47150</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8141,12 +8141,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8161,12 +8161,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16987</t>
+          <t>16412</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34668</t>
+          <t>35016</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8176,12 +8176,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8196,12 +8196,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46563</t>
+          <t>46117</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75167</t>
+          <t>74479</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,23%</t>
         </is>
       </c>
     </row>
@@ -8239,12 +8239,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>75793</t>
+          <t>75889</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>103076</t>
+          <t>102076</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>59,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8274,12 +8274,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59100</t>
+          <t>58448</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>79504</t>
+          <t>79254</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>69,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8309,12 +8309,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>141668</t>
+          <t>142293</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>174956</t>
+          <t>175620</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>61,84%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10204</t>
+          <t>9251</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5859</t>
+          <t>6015</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1782</t>
+          <t>1879</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11415</t>
+          <t>12373</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -8582,12 +8582,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>852</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6491</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8597,12 +8597,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1821</t>
+          <t>1904</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12209</t>
+          <t>12615</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>3598</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15031</t>
+          <t>15169</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -8695,12 +8695,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14600</t>
+          <t>14293</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>30867</t>
+          <t>31133</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10336</t>
+          <t>10345</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25410</t>
+          <t>25091</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8745,12 +8745,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>29286</t>
+          <t>28177</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>51129</t>
+          <t>49745</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8780,12 +8780,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>23,61%</t>
         </is>
       </c>
     </row>
@@ -8808,12 +8808,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>34458</t>
+          <t>34287</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>54263</t>
+          <t>54277</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8823,12 +8823,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8843,12 +8843,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17159</t>
+          <t>17915</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34057</t>
+          <t>34751</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>56897</t>
+          <t>56115</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>82123</t>
+          <t>82135</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,98%</t>
         </is>
       </c>
     </row>
@@ -8921,12 +8921,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>44411</t>
+          <t>44218</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>66826</t>
+          <t>66674</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8936,12 +8936,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>52,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8956,12 +8956,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26454</t>
+          <t>25498</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>44193</t>
+          <t>43674</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8991,12 +8991,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>75162</t>
+          <t>76985</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>103039</t>
+          <t>105519</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>48,9%</t>
+          <t>50,08%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>942</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7985</t>
+          <t>8234</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1524</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11533</t>
+          <t>10940</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3140</t>
+          <t>3183</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14456</t>
+          <t>16109</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>8,3%</t>
         </is>
       </c>
     </row>
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>986</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>10095</t>
+          <t>9979</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9284,7 +9284,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9299,12 +9299,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9334,12 +9334,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>976</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>10366</t>
+          <t>9815</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -9377,12 +9377,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2877</t>
+          <t>3144</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>13418</t>
+          <t>14042</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9412,12 +9412,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3018</t>
+          <t>2951</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14094</t>
+          <t>14013</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8745</t>
+          <t>8246</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>23442</t>
+          <t>22518</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -9490,12 +9490,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3105</t>
+          <t>3162</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15007</t>
+          <t>15657</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9505,12 +9505,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4548</t>
+          <t>4615</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16293</t>
+          <t>16875</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10220</t>
+          <t>10048</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>26690</t>
+          <t>26258</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -9603,12 +9603,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>81174</t>
+          <t>80166</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>98376</t>
+          <t>98108</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9618,12 +9618,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9638,12 +9638,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>52504</t>
+          <t>52133</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>67652</t>
+          <t>67780</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>63,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>138430</t>
+          <t>136810</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>162022</t>
+          <t>161307</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,13%</t>
         </is>
       </c>
     </row>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>5096</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9868,62 +9868,62 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>957</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>1768</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>5863</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>957</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>4817</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -9946,97 +9946,97 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>2632</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>798</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>7163</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>4,75%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>12,93%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>2632</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>1938</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>6811</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>2,39%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>2632</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>811</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>7206</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>4,75%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>13,0%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>2632</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>821</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>7601</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -10059,12 +10059,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>12547</t>
+          <t>13514</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>27986</t>
+          <t>29362</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>10359</t>
+          <t>9499</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>22821</t>
+          <t>22331</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>26737</t>
+          <t>26807</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>47076</t>
+          <t>48640</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>35,67%</t>
         </is>
       </c>
     </row>
@@ -10172,12 +10172,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>29231</t>
+          <t>28790</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>47191</t>
+          <t>46297</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10187,12 +10187,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>16812</t>
+          <t>17153</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>30996</t>
+          <t>30876</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>55,71%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10242,12 +10242,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>50521</t>
+          <t>49929</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>72359</t>
+          <t>72523</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>53,19%</t>
         </is>
       </c>
     </row>
@@ -10285,12 +10285,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>14409</t>
+          <t>14706</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>30298</t>
+          <t>31298</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -10300,12 +10300,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>7997</t>
+          <t>7903</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>20438</t>
+          <t>20076</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>25913</t>
+          <t>25645</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>47175</t>
+          <t>45877</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>33,65%</t>
         </is>
       </c>
     </row>
@@ -10515,97 +10515,97 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>2323</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>1981</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>7362</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>9,74%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>2323</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
+      <c r="S34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>7809</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>8020</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>10,33%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>2323</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>8131</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -10628,12 +10628,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6781</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>20985</t>
+          <t>19748</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10643,12 +10643,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10663,12 +10663,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>6518</t>
+          <t>7158</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>19387</t>
+          <t>19721</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10678,12 +10678,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10698,12 +10698,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>16160</t>
+          <t>16993</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>34241</t>
+          <t>34485</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10713,12 +10713,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,84%</t>
         </is>
       </c>
     </row>
@@ -10741,12 +10741,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>26619</t>
+          <t>26438</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>46008</t>
+          <t>45022</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10756,12 +10756,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10776,12 +10776,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>14161</t>
+          <t>14019</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>28903</t>
+          <t>28733</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10791,12 +10791,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10811,12 +10811,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>43802</t>
+          <t>44424</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>69032</t>
+          <t>69954</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10826,12 +10826,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>38,21%</t>
         </is>
       </c>
     </row>
@@ -10854,12 +10854,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>20970</t>
+          <t>20851</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>39440</t>
+          <t>39255</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10889,12 +10889,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>19518</t>
+          <t>18774</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>35986</t>
+          <t>34825</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10904,12 +10904,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>44704</t>
+          <t>44650</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>69154</t>
+          <t>69341</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10939,12 +10939,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,88%</t>
         </is>
       </c>
     </row>
@@ -10967,12 +10967,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>21407</t>
+          <t>21192</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>39542</t>
+          <t>39546</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10982,12 +10982,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>36,78%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -11002,12 +11002,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>7950</t>
+          <t>7754</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>21670</t>
+          <t>22279</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -11017,12 +11017,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -11037,12 +11037,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>32662</t>
+          <t>32912</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>57411</t>
+          <t>56310</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -11052,12 +11052,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>30,76%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>9784</t>
+          <t>9557</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>26438</t>
+          <t>26792</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>5623</t>
+          <t>5410</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>19434</t>
+          <t>19066</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>18245</t>
+          <t>17768</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>39280</t>
+          <t>38653</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -11310,12 +11310,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>24584</t>
+          <t>25521</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>47590</t>
+          <t>48956</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11325,12 +11325,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11345,12 +11345,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>26235</t>
+          <t>27194</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>49433</t>
+          <t>49809</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11360,12 +11360,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11380,12 +11380,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>56198</t>
+          <t>56065</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>90124</t>
+          <t>90309</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11395,12 +11395,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -11423,12 +11423,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>84474</t>
+          <t>84848</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>121598</t>
+          <t>120966</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>53263</t>
+          <t>53143</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>80925</t>
+          <t>82086</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11493,12 +11493,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>146763</t>
+          <t>147735</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>192563</t>
+          <t>195454</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11508,12 +11508,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>30,31%</t>
         </is>
       </c>
     </row>
@@ -11536,12 +11536,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>66351</t>
+          <t>65316</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>98747</t>
+          <t>99616</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>59528</t>
+          <t>59805</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>90673</t>
+          <t>89413</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -11606,12 +11606,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>134524</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>181165</t>
+          <t>180791</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11621,12 +11621,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,04%</t>
         </is>
       </c>
     </row>
@@ -11649,12 +11649,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>106427</t>
+          <t>106745</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>145855</t>
+          <t>144253</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>80343</t>
+          <t>79298</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>114493</t>
+          <t>112580</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -11699,12 +11699,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>198273</t>
+          <t>196042</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>247937</t>
+          <t>248129</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11734,12 +11734,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,48%</t>
         </is>
       </c>
     </row>
@@ -11879,12 +11879,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>2003</t>
+          <t>1952</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>13055</t>
+          <t>12257</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11919,7 +11919,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>5781</t>
+          <t>5134</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11949,12 +11949,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>2918</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>13583</t>
+          <t>14146</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11964,12 +11964,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -11997,7 +11997,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>4672</t>
+          <t>4822</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12012,7 +12012,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12027,12 +12027,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1087</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>9791</t>
+          <t>9426</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12062,12 +12062,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>10227</t>
+          <t>11601</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12082,7 +12082,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -12105,12 +12105,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>26338</t>
+          <t>27269</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>49536</t>
+          <t>51777</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12120,12 +12120,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12140,12 +12140,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>21296</t>
+          <t>21789</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>42016</t>
+          <t>42567</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12155,12 +12155,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12175,12 +12175,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>54888</t>
+          <t>54659</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>86846</t>
+          <t>84689</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12190,12 +12190,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>14,87%</t>
         </is>
       </c>
     </row>
@@ -12218,12 +12218,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>97402</t>
+          <t>97955</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>133728</t>
+          <t>132935</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12233,12 +12233,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,78%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>40,41%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>75586</t>
+          <t>75585</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>106823</t>
+          <t>105320</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12273,7 +12273,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12288,12 +12288,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>181848</t>
+          <t>179051</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>228876</t>
+          <t>226707</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12303,12 +12303,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>39,81%</t>
         </is>
       </c>
     </row>
@@ -12331,12 +12331,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>150283</t>
+          <t>150992</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>187524</t>
+          <t>187867</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>98609</t>
+          <t>98034</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>131008</t>
+          <t>129572</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -12381,12 +12381,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>40,77%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>53,88%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -12401,12 +12401,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>257683</t>
+          <t>261763</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>308867</t>
+          <t>309431</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -12416,12 +12416,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>54,34%</t>
         </is>
       </c>
     </row>
@@ -12561,12 +12561,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>27043</t>
+          <t>26995</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>52696</t>
+          <t>53451</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12581,7 +12581,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12596,12 +12596,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>17794</t>
+          <t>18335</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>39113</t>
+          <t>39168</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12611,12 +12611,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12631,12 +12631,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>50873</t>
+          <t>51436</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>83482</t>
+          <t>85397</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12646,12 +12646,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -12674,12 +12674,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>59030</t>
+          <t>58090</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>97659</t>
+          <t>95612</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12689,12 +12689,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12709,12 +12709,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>59474</t>
+          <t>60045</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>91949</t>
+          <t>91511</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12724,12 +12724,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12744,12 +12744,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>127092</t>
+          <t>125572</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>175290</t>
+          <t>172949</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12759,12 +12759,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -12787,12 +12787,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>255462</t>
+          <t>254758</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>318984</t>
+          <t>317637</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12802,12 +12802,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12822,12 +12822,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>162240</t>
+          <t>161096</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>209433</t>
+          <t>210266</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12837,12 +12837,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12857,12 +12857,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>434669</t>
+          <t>430047</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>508551</t>
+          <t>509790</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12872,12 +12872,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,73%</t>
         </is>
       </c>
     </row>
@@ -12900,12 +12900,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>346522</t>
+          <t>345810</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>417308</t>
+          <t>410788</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12935,12 +12935,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>265089</t>
+          <t>267257</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>324239</t>
+          <t>327275</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12950,12 +12950,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12970,12 +12970,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>622867</t>
+          <t>623586</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>713638</t>
+          <t>715936</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12985,12 +12985,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>29,02%</t>
+          <t>29,11%</t>
         </is>
       </c>
     </row>
@@ -13013,12 +13013,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>602258</t>
+          <t>605890</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>680039</t>
+          <t>683259</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13028,12 +13028,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13048,12 +13048,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>429776</t>
+          <t>424681</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>492566</t>
+          <t>489448</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13063,12 +13063,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13083,12 +13083,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1053904</t>
+          <t>1048893</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>1152704</t>
+          <t>1155843</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13098,12 +13098,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>47,0%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P6714-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P6714-Provincia-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1847</t>
+          <t>1653</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10066</t>
+          <t>9976</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1099</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10140</t>
+          <t>9393</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3764</t>
+          <t>3755</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15279</t>
+          <t>15703</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2457</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14493</t>
+          <t>14680</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1140</t>
+          <t>1165</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9657</t>
+          <t>9688</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4820</t>
+          <t>4848</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19655</t>
+          <t>19635</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10893</t>
+          <t>10927</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>28660</t>
+          <t>28560</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3335</t>
+          <t>3425</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14366</t>
+          <t>15060</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17602</t>
+          <t>17526</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>39466</t>
+          <t>38987</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,19%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5241</t>
+          <t>5836</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18495</t>
+          <t>19810</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4219</t>
+          <t>4269</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15926</t>
+          <t>16201</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12638</t>
+          <t>12781</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30096</t>
+          <t>30168</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,07%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>74574</t>
+          <t>74127</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>96380</t>
+          <t>95378</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>58,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53750</t>
+          <t>54094</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>71021</t>
+          <t>70890</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>61,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>133749</t>
+          <t>133518</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>162864</t>
+          <t>161696</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>75,43%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9540</t>
+          <t>10734</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>944</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8219</t>
+          <t>8332</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3232</t>
+          <t>2996</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14635</t>
+          <t>13841</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9369</t>
+          <t>9708</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8875</t>
+          <t>10560</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2876</t>
+          <t>2849</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14577</t>
+          <t>15263</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6871</t>
+          <t>6691</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21620</t>
+          <t>20987</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3432</t>
+          <t>3430</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15934</t>
+          <t>15511</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>12846</t>
+          <t>12872</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>31363</t>
+          <t>31161</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,57%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10385</t>
+          <t>10773</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27440</t>
+          <t>27303</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13152</t>
+          <t>13220</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31145</t>
+          <t>30810</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>27716</t>
+          <t>27831</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50524</t>
+          <t>53153</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>18,02%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>120468</t>
+          <t>121315</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>143030</t>
+          <t>144079</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>70,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>76508</t>
+          <t>76003</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>97280</t>
+          <t>96647</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>78,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>204596</t>
+          <t>203177</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>234735</t>
+          <t>235636</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>68,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,9%</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10362</t>
+          <t>10479</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4595</t>
+          <t>5209</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>919</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11641</t>
+          <t>11671</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>940</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9274</t>
+          <t>8498</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>947</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7794</t>
+          <t>7761</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2854</t>
+          <t>2829</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13221</t>
+          <t>13347</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10308</t>
+          <t>10401</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25403</t>
+          <t>25949</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>12126</t>
+          <t>12313</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27956</t>
+          <t>28612</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>26341</t>
+          <t>26521</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>48371</t>
+          <t>49620</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>22,1%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29395</t>
+          <t>29388</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50415</t>
+          <t>50974</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11938</t>
+          <t>12866</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27373</t>
+          <t>27441</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>47589</t>
+          <t>45003</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>72558</t>
+          <t>73058</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,54%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>67814</t>
+          <t>67712</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>90957</t>
+          <t>91289</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30614</t>
+          <t>29539</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>48114</t>
+          <t>48023</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>59,18%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>102949</t>
+          <t>104319</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>133175</t>
+          <t>134365</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,85%</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5270</t>
+          <t>5758</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,7 +2797,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4573</t>
+          <t>5192</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1063</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13322</t>
+          <t>13474</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>1121</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9937</t>
+          <t>9942</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3616</t>
+          <t>3393</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>17095</t>
+          <t>17597</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11300</t>
+          <t>11046</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>28455</t>
+          <t>27942</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13972</t>
+          <t>13729</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>31344</t>
+          <t>30600</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>28203</t>
+          <t>28547</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>54146</t>
+          <t>52678</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>21,66%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>26856</t>
+          <t>26991</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>48807</t>
+          <t>48519</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13663</t>
+          <t>13896</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>29892</t>
+          <t>29439</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>45006</t>
+          <t>44352</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>73183</t>
+          <t>70500</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>28,98%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>69832</t>
+          <t>68573</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>95020</t>
+          <t>95228</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>43600</t>
+          <t>43750</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>64138</t>
+          <t>64197</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>120159</t>
+          <t>120478</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>153292</t>
+          <t>152686</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>49,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>63,02%</t>
+          <t>62,77%</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7148</t>
+          <t>6598</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6166</t>
+          <t>6631</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>969</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>9152</t>
+          <t>10056</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,29%</t>
         </is>
       </c>
     </row>
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1784</t>
+          <t>1846</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12102</t>
+          <t>11083</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1192</t>
+          <t>1214</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>12450</t>
+          <t>12940</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,38%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6904</t>
+          <t>6601</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>21113</t>
+          <t>20141</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>8515</t>
+          <t>8815</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>21271</t>
+          <t>22550</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>18309</t>
+          <t>18662</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>37959</t>
+          <t>37392</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,11%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>9387</t>
+          <t>9617</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>23130</t>
+          <t>23833</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>5965</t>
+          <t>5739</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>17610</t>
+          <t>17189</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>17846</t>
+          <t>18444</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>35801</t>
+          <t>36695</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,6%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>42603</t>
+          <t>43416</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>60955</t>
+          <t>60823</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>52,74%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>15927</t>
+          <t>16357</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>30520</t>
+          <t>30547</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>64140</t>
+          <t>62259</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>87879</t>
+          <t>87258</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>63,25%</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>5988</t>
+          <t>6695</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>7374</t>
+          <t>8238</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>10349</t>
+          <t>10422</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>9830</t>
+          <t>10120</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>25227</t>
+          <t>25033</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>5971</t>
+          <t>5655</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>18041</t>
+          <t>17424</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>19253</t>
+          <t>19405</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>37666</t>
+          <t>39476</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>22,75%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>12346</t>
+          <t>12631</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>30157</t>
+          <t>30899</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>5893</t>
+          <t>5925</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>17752</t>
+          <t>17924</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,42%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>21880</t>
+          <t>21831</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>43732</t>
+          <t>42679</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>24,59%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>68701</t>
+          <t>68381</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>90014</t>
+          <t>89623</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>57,82%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>23460</t>
+          <t>23755</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>38585</t>
+          <t>38421</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,96%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>97050</t>
+          <t>96393</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>122774</t>
+          <t>123870</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>71,37%</t>
         </is>
       </c>
     </row>
@@ -4828,7 +4828,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>6886</t>
+          <t>6073</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4843,7 +4843,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>1892</t>
+          <t>1891</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>10807</t>
+          <t>11296</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>2907</t>
+          <t>3002</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>13799</t>
+          <t>14019</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -4936,12 +4936,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>7039</t>
+          <t>7465</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>22816</t>
+          <t>23961</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4951,12 +4951,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>5388</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>19514</t>
+          <t>19778</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>16654</t>
+          <t>15856</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>36806</t>
+          <t>36681</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,11%</t>
         </is>
       </c>
     </row>
@@ -5049,12 +5049,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>39898</t>
+          <t>39311</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>66897</t>
+          <t>66480</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>27031</t>
+          <t>26296</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>50119</t>
+          <t>49541</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>70843</t>
+          <t>71982</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>107316</t>
+          <t>108628</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>24,03%</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5162,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>40070</t>
+          <t>40003</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>67323</t>
+          <t>67479</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5177,12 +5177,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>30314</t>
+          <t>31271</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>53625</t>
+          <t>53314</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>76513</t>
+          <t>76423</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>111438</t>
+          <t>112315</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,84%</t>
         </is>
       </c>
     </row>
@@ -5275,12 +5275,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>132763</t>
+          <t>131664</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>165008</t>
+          <t>167285</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>61,97%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>74087</t>
+          <t>74669</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>101938</t>
+          <t>101032</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5325,12 +5325,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>214471</t>
+          <t>214125</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>259975</t>
+          <t>258933</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5360,12 +5360,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>57,27%</t>
         </is>
       </c>
     </row>
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>11092</t>
+          <t>11364</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5525,7 +5525,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5545,7 +5545,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>9589</t>
+          <t>9029</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5560,7 +5560,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>4072</t>
+          <t>4122</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>16595</t>
+          <t>17100</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>8656</t>
+          <t>8448</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>26236</t>
+          <t>26068</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>3096</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>16138</t>
+          <t>17073</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>14895</t>
+          <t>14733</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>35739</t>
+          <t>37626</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>34525</t>
+          <t>34255</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>62809</t>
+          <t>63165</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>25281</t>
+          <t>25095</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>47724</t>
+          <t>49746</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>65832</t>
+          <t>65728</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>99910</t>
+          <t>100034</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,09%</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>109583</t>
+          <t>110053</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>147962</t>
+          <t>146826</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>89854</t>
+          <t>88956</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>122656</t>
+          <t>122651</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>211413</t>
+          <t>209912</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>260520</t>
+          <t>258706</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>41,61%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>145190</t>
+          <t>147544</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>186826</t>
+          <t>187455</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>90307</t>
+          <t>91139</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>123668</t>
+          <t>124169</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>47,64%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>247233</t>
+          <t>250119</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>298187</t>
+          <t>300117</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>48,27%</t>
         </is>
       </c>
     </row>
@@ -6187,12 +6187,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>14481</t>
+          <t>13742</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>33441</t>
+          <t>34170</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6202,82 +6202,82 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>17738</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>10488</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>27858</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>1,88%</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>2,95%</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr">
+        <is>
+          <t>40287</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>30285</t>
+        </is>
+      </c>
+      <c r="T52" s="2" t="inlineStr">
+        <is>
+          <t>55743</t>
+        </is>
+      </c>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
           <t>2,36%</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>17738</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>10896</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr">
-        <is>
-          <t>28388</t>
-        </is>
-      </c>
-      <c r="N52" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
-      <c r="O52" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="P52" s="2" t="inlineStr">
-        <is>
-          <t>3,0%</t>
-        </is>
-      </c>
-      <c r="Q52" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="R52" s="2" t="inlineStr">
-        <is>
-          <t>40287</t>
-        </is>
-      </c>
-      <c r="S52" s="2" t="inlineStr">
-        <is>
-          <t>28500</t>
-        </is>
-      </c>
-      <c r="T52" s="2" t="inlineStr">
-        <is>
-          <t>55319</t>
-        </is>
-      </c>
-      <c r="U52" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="V52" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="W52" s="2" t="inlineStr">
-        <is>
-          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -6300,12 +6300,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>37814</t>
+          <t>37009</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>66223</t>
+          <t>66184</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6315,7 +6315,7 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
@@ -6335,12 +6335,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>28133</t>
+          <t>28576</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>55537</t>
+          <t>55752</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>72187</t>
+          <t>71279</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>113893</t>
+          <t>112385</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -6413,12 +6413,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>168176</t>
+          <t>168757</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>221423</t>
+          <t>224994</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6428,12 +6428,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>133635</t>
+          <t>132604</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>177963</t>
+          <t>182021</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6483,12 +6483,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>314423</t>
+          <t>316369</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>388836</t>
+          <t>386894</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,38%</t>
         </is>
       </c>
     </row>
@@ -6526,12 +6526,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>291319</t>
+          <t>288603</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>359715</t>
+          <t>357218</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6561,12 +6561,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>213748</t>
+          <t>212703</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>267521</t>
+          <t>267655</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6596,12 +6596,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>520028</t>
+          <t>521384</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>605764</t>
+          <t>603596</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,55%</t>
         </is>
       </c>
     </row>
@@ -6639,12 +6639,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>788887</t>
+          <t>789635</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>865000</t>
+          <t>867498</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>55,64%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6674,12 +6674,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>460768</t>
+          <t>459151</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>524402</t>
+          <t>522657</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>48,6%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6709,12 +6709,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1268668</t>
+          <t>1272053</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>1371607</t>
+          <t>1370481</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>58,01%</t>
         </is>
       </c>
     </row>
@@ -7105,12 +7105,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2722</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14394</t>
+          <t>14290</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>942</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10328</t>
+          <t>9234</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>5423</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19841</t>
+          <t>19752</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -7218,12 +7218,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8256</t>
+          <t>8337</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24004</t>
+          <t>24250</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7233,12 +7233,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>2157</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12478</t>
+          <t>12183</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12913</t>
+          <t>12254</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32084</t>
+          <t>31185</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7303,12 +7303,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,15%</t>
         </is>
       </c>
     </row>
@@ -7331,12 +7331,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16536</t>
+          <t>15540</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36103</t>
+          <t>35247</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7346,12 +7346,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9657</t>
+          <t>8937</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24162</t>
+          <t>22584</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7381,12 +7381,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>29687</t>
+          <t>30194</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>54351</t>
+          <t>53462</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,54%</t>
         </is>
       </c>
     </row>
@@ -7444,12 +7444,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17217</t>
+          <t>18453</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36807</t>
+          <t>37481</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12469</t>
+          <t>12611</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29123</t>
+          <t>30036</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7494,12 +7494,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>33521</t>
+          <t>34323</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60110</t>
+          <t>61024</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7529,12 +7529,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,73%</t>
         </is>
       </c>
     </row>
@@ -7557,12 +7557,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>50476</t>
+          <t>50501</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>74680</t>
+          <t>74286</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>46252</t>
+          <t>45783</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>65965</t>
+          <t>65909</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7607,12 +7607,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>102958</t>
+          <t>102173</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>134147</t>
+          <t>134137</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7642,12 +7642,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>56,56%</t>
         </is>
       </c>
     </row>
@@ -7792,7 +7792,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7454</t>
+          <t>7467</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>986</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8324</t>
+          <t>9403</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2032</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11806</t>
+          <t>11679</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -7900,12 +7900,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11353</t>
+          <t>11451</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2385</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13203</t>
+          <t>13153</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6331</t>
+          <t>6486</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>20421</t>
+          <t>20887</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -8013,12 +8013,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27851</t>
+          <t>27469</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>49668</t>
+          <t>49840</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8028,12 +8028,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5081</t>
+          <t>5156</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17540</t>
+          <t>17788</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>36166</t>
+          <t>35826</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>63513</t>
+          <t>61542</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>21,67%</t>
         </is>
       </c>
     </row>
@@ -8126,12 +8126,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25995</t>
+          <t>26823</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>47150</t>
+          <t>48507</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8141,12 +8141,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8161,12 +8161,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16412</t>
+          <t>17004</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35016</t>
+          <t>34479</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8176,12 +8176,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8196,12 +8196,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46117</t>
+          <t>47665</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74479</t>
+          <t>74780</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -8239,12 +8239,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>75889</t>
+          <t>75951</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>102076</t>
+          <t>102720</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8274,12 +8274,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>58448</t>
+          <t>57831</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>79254</t>
+          <t>79192</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8309,12 +8309,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>142293</t>
+          <t>141662</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>175620</t>
+          <t>175651</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>61,85%</t>
         </is>
       </c>
     </row>
@@ -8469,62 +8469,62 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>870</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>9961</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,69%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>7,88%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1898</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>9251</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5912</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>1898</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>6015</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1879</t>
+          <t>1830</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12373</t>
+          <t>11438</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -8582,12 +8582,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>857</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>7961</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8597,12 +8597,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1904</t>
+          <t>1727</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12615</t>
+          <t>11197</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3598</t>
+          <t>3605</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15169</t>
+          <t>15515</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8672,7 +8672,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -8695,12 +8695,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14293</t>
+          <t>14755</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>31133</t>
+          <t>32104</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10345</t>
+          <t>9696</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>25091</t>
+          <t>24848</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8745,12 +8745,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>28177</t>
+          <t>28768</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>49745</t>
+          <t>50688</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8780,12 +8780,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -8808,12 +8808,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>34287</t>
+          <t>33525</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>54277</t>
+          <t>54087</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8823,12 +8823,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,95%</t>
+          <t>42,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8843,12 +8843,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17915</t>
+          <t>18372</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34751</t>
+          <t>35712</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>56115</t>
+          <t>55976</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>82135</t>
+          <t>83317</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>39,54%</t>
         </is>
       </c>
     </row>
@@ -8921,12 +8921,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>44218</t>
+          <t>43131</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>66674</t>
+          <t>65400</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8936,12 +8936,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>51,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8956,12 +8956,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25498</t>
+          <t>25952</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43674</t>
+          <t>43433</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8991,12 +8991,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>76985</t>
+          <t>74647</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>105519</t>
+          <t>102628</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>48,7%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>939</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8234</t>
+          <t>7537</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1524</t>
+          <t>1559</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10940</t>
+          <t>11554</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3183</t>
+          <t>3092</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>16109</t>
+          <t>15123</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>7,79%</t>
         </is>
       </c>
     </row>
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>998</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9979</t>
+          <t>11337</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9334,12 +9334,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>998</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>9815</t>
+          <t>10474</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,4%</t>
         </is>
       </c>
     </row>
@@ -9377,12 +9377,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3144</t>
+          <t>2828</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>14042</t>
+          <t>14012</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9412,12 +9412,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14013</t>
+          <t>14068</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>8246</t>
+          <t>8150</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>22518</t>
+          <t>23141</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,93%</t>
         </is>
       </c>
     </row>
@@ -9490,12 +9490,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3162</t>
+          <t>3134</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15657</t>
+          <t>15917</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9505,12 +9505,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4615</t>
+          <t>4907</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16875</t>
+          <t>17051</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10048</t>
+          <t>10764</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>26258</t>
+          <t>26742</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,78%</t>
         </is>
       </c>
     </row>
@@ -9603,12 +9603,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>80166</t>
+          <t>79869</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>98108</t>
+          <t>98259</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9618,12 +9618,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9638,12 +9638,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>52133</t>
+          <t>51879</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>67780</t>
+          <t>67919</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>136810</t>
+          <t>137962</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>161307</t>
+          <t>162090</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>83,53%</t>
         </is>
       </c>
     </row>
@@ -9838,7 +9838,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5096</t>
+          <t>4612</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5863</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9923,7 +9923,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -9981,12 +9981,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>813</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>7163</t>
+          <t>7216</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>819</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6811</t>
+          <t>7144</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -10059,12 +10059,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>13514</t>
+          <t>12466</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>29362</t>
+          <t>28484</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>9499</t>
+          <t>10757</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>22331</t>
+          <t>23343</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>26807</t>
+          <t>26944</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>48640</t>
+          <t>47814</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>35,07%</t>
         </is>
       </c>
     </row>
@@ -10172,12 +10172,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>28790</t>
+          <t>29019</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>46297</t>
+          <t>47373</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10187,12 +10187,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>58,54%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>17153</t>
+          <t>16888</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>30876</t>
+          <t>30723</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,44%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10242,12 +10242,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>49929</t>
+          <t>49849</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>72523</t>
+          <t>72693</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>53,31%</t>
         </is>
       </c>
     </row>
@@ -10285,12 +10285,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>14706</t>
+          <t>14836</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>31298</t>
+          <t>32250</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -10300,12 +10300,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>7903</t>
+          <t>7790</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>20076</t>
+          <t>20558</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>25645</t>
+          <t>25072</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>45877</t>
+          <t>45868</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,64%</t>
         </is>
       </c>
     </row>
@@ -10555,7 +10555,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>7362</t>
+          <t>7929</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10570,7 +10570,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>8020</t>
+          <t>7897</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10605,7 +10605,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -10628,12 +10628,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6982</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>19748</t>
+          <t>20593</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10643,12 +10643,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10663,12 +10663,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>7158</t>
+          <t>6598</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>19721</t>
+          <t>18893</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10678,12 +10678,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10698,12 +10698,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>16993</t>
+          <t>16316</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>34485</t>
+          <t>34300</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10713,12 +10713,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,74%</t>
         </is>
       </c>
     </row>
@@ -10741,12 +10741,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>26438</t>
+          <t>26334</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>45022</t>
+          <t>44754</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10756,12 +10756,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10776,12 +10776,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>14019</t>
+          <t>13502</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>28733</t>
+          <t>28330</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10791,12 +10791,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10811,12 +10811,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>44424</t>
+          <t>44676</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>69954</t>
+          <t>70280</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10826,12 +10826,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>38,39%</t>
         </is>
       </c>
     </row>
@@ -10854,12 +10854,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>20851</t>
+          <t>21574</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>39255</t>
+          <t>39732</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10889,12 +10889,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>18774</t>
+          <t>19549</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>34825</t>
+          <t>35208</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10904,12 +10904,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>44650</t>
+          <t>44680</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>69341</t>
+          <t>70779</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10939,12 +10939,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>38,66%</t>
         </is>
       </c>
     </row>
@@ -10967,12 +10967,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>21192</t>
+          <t>21642</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>39546</t>
+          <t>40444</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10982,12 +10982,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -11002,12 +11002,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>7754</t>
+          <t>7609</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>22279</t>
+          <t>21486</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -11017,12 +11017,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -11037,12 +11037,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>32912</t>
+          <t>31890</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>56310</t>
+          <t>55697</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -11052,12 +11052,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,42%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>9557</t>
+          <t>9101</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>26792</t>
+          <t>25641</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>5410</t>
+          <t>5572</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>19066</t>
+          <t>19617</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>17768</t>
+          <t>18420</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>38653</t>
+          <t>40131</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -11310,12 +11310,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>25521</t>
+          <t>24918</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>48956</t>
+          <t>48662</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11325,12 +11325,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11345,12 +11345,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>27194</t>
+          <t>27768</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>49809</t>
+          <t>50423</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11360,12 +11360,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11380,12 +11380,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>56065</t>
+          <t>57764</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>90309</t>
+          <t>89577</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11395,12 +11395,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,89%</t>
         </is>
       </c>
     </row>
@@ -11423,12 +11423,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>84848</t>
+          <t>83719</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>120966</t>
+          <t>121488</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>53143</t>
+          <t>53806</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>82086</t>
+          <t>81528</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11493,12 +11493,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>147735</t>
+          <t>145398</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>195454</t>
+          <t>191555</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11508,12 +11508,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>29,71%</t>
         </is>
       </c>
     </row>
@@ -11536,12 +11536,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>65316</t>
+          <t>64108</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>99616</t>
+          <t>97050</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>59805</t>
+          <t>59639</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>89413</t>
+          <t>90177</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -11606,12 +11606,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>134524</t>
+          <t>134103</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>180791</t>
+          <t>177169</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11621,12 +11621,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>27,48%</t>
         </is>
       </c>
     </row>
@@ -11649,12 +11649,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>106745</t>
+          <t>106037</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>144253</t>
+          <t>145917</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>79298</t>
+          <t>79485</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>112580</t>
+          <t>111542</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -11699,12 +11699,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>196042</t>
+          <t>195018</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>248129</t>
+          <t>247153</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11734,12 +11734,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,33%</t>
         </is>
       </c>
     </row>
@@ -11884,7 +11884,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>12257</t>
+          <t>12308</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11899,7 +11899,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11919,7 +11919,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>5134</t>
+          <t>5790</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11949,12 +11949,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>2918</t>
+          <t>2479</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>14146</t>
+          <t>14108</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11964,7 +11964,7 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -11997,7 +11997,7 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>4822</t>
+          <t>3984</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12012,7 +12012,7 @@
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12027,12 +12027,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>1077</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>9426</t>
+          <t>9447</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12062,12 +12062,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>11601</t>
+          <t>11180</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -12105,12 +12105,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>27269</t>
+          <t>27175</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>51777</t>
+          <t>49872</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12120,12 +12120,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12140,12 +12140,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>21789</t>
+          <t>21918</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>42567</t>
+          <t>41717</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12155,12 +12155,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12175,12 +12175,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>54659</t>
+          <t>53086</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>84689</t>
+          <t>86851</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12190,12 +12190,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,25%</t>
         </is>
       </c>
     </row>
@@ -12218,12 +12218,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>97955</t>
+          <t>96135</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>132935</t>
+          <t>131945</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12233,12 +12233,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>75585</t>
+          <t>75891</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>105320</t>
+          <t>105120</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12268,12 +12268,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12288,12 +12288,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>179051</t>
+          <t>183003</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>226707</t>
+          <t>227817</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12303,12 +12303,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>40,01%</t>
         </is>
       </c>
     </row>
@@ -12331,12 +12331,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>150992</t>
+          <t>152348</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>187867</t>
+          <t>188843</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>98034</t>
+          <t>99933</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>129572</t>
+          <t>129356</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -12381,12 +12381,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -12401,12 +12401,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>261763</t>
+          <t>259242</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>309431</t>
+          <t>307895</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -12416,12 +12416,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>54,07%</t>
         </is>
       </c>
     </row>
@@ -12561,12 +12561,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>26995</t>
+          <t>27060</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>53451</t>
+          <t>53344</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12581,7 +12581,7 @@
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12596,12 +12596,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>18335</t>
+          <t>18019</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>39168</t>
+          <t>39567</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12611,12 +12611,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12631,12 +12631,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>51436</t>
+          <t>51590</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>85397</t>
+          <t>85485</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12646,12 +12646,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -12674,12 +12674,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>58090</t>
+          <t>58390</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>95612</t>
+          <t>93531</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12689,12 +12689,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12709,12 +12709,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>60045</t>
+          <t>59426</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>91511</t>
+          <t>92233</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12724,12 +12724,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12744,12 +12744,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>125572</t>
+          <t>127148</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>172949</t>
+          <t>175728</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12759,12 +12759,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -12787,12 +12787,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>254758</t>
+          <t>257661</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>317637</t>
+          <t>319836</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12802,12 +12802,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12822,12 +12822,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>161096</t>
+          <t>160892</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>210266</t>
+          <t>210549</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12837,12 +12837,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12857,12 +12857,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>430047</t>
+          <t>430212</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>509790</t>
+          <t>514825</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12877,7 +12877,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,93%</t>
         </is>
       </c>
     </row>
@@ -12900,12 +12900,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>345810</t>
+          <t>346519</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>410788</t>
+          <t>415395</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12935,12 +12935,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>267257</t>
+          <t>264339</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>327275</t>
+          <t>323364</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12950,12 +12950,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12970,12 +12970,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>623586</t>
+          <t>624891</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>715936</t>
+          <t>712366</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12985,12 +12985,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>28,96%</t>
         </is>
       </c>
     </row>
@@ -13013,12 +13013,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>605890</t>
+          <t>607478</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>683259</t>
+          <t>686802</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13028,12 +13028,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13048,12 +13048,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>424681</t>
+          <t>425403</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>489448</t>
+          <t>490477</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13063,12 +13063,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>47,29%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13083,12 +13083,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1048893</t>
+          <t>1050849</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>1155843</t>
+          <t>1150343</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13098,12 +13098,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>46,77%</t>
         </is>
       </c>
     </row>
